--- a/data/extracted/inventory-receipts/CONTENEDOR FRIA 240 26 MAYO.xlsx
+++ b/data/extracted/inventory-receipts/CONTENEDOR FRIA 240 26 MAYO.xlsx
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE74242B-972B-4D8C-917A-F020057ED3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9135"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -3896,7 +3909,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -3937,11 +3950,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4222,50 +4234,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L989"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -4303,12 +4315,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -4346,7 +4358,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -4384,7 +4396,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -4422,7 +4434,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -4460,7 +4472,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -4498,7 +4510,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -4536,7 +4548,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -4574,7 +4586,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -4612,7 +4624,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -4650,7 +4662,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -4688,7 +4700,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -4726,7 +4738,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -4764,7 +4776,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -4802,7 +4814,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -4840,7 +4852,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -4878,7 +4890,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -4916,7 +4928,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -4954,7 +4966,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -4992,7 +5004,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -5030,7 +5042,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -5068,7 +5080,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -5106,7 +5118,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -5144,7 +5156,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -5182,7 +5194,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -5220,7 +5232,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -5258,7 +5270,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -5296,7 +5308,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -5334,7 +5346,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -5372,7 +5384,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -5410,7 +5422,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -5448,7 +5460,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -5486,7 +5498,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -5524,7 +5536,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -5562,7 +5574,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -5600,7 +5612,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -5638,7 +5650,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -5676,7 +5688,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -5714,7 +5726,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -5752,7 +5764,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -5790,7 +5802,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -5828,7 +5840,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -5866,7 +5878,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -5904,7 +5916,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -5942,7 +5954,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -5980,7 +5992,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -6018,7 +6030,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -6056,7 +6068,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -6094,7 +6106,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -6132,7 +6144,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -6170,7 +6182,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -6208,7 +6220,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -6246,7 +6258,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -6284,7 +6296,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -6322,7 +6334,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -6360,7 +6372,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -6398,7 +6410,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -6436,7 +6448,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -6474,7 +6486,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6512,7 +6524,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -6550,7 +6562,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -6588,7 +6600,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -6626,7 +6638,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -6664,7 +6676,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -6702,7 +6714,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -6740,7 +6752,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F71" s="1" t="s">
         <v>153</v>
       </c>
@@ -6760,7 +6772,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F72" s="1" t="s">
         <v>155</v>
       </c>
@@ -6780,7 +6792,7 @@
         <v>1456.5</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -6818,7 +6830,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -6856,7 +6868,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -6894,7 +6906,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -6932,7 +6944,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -6970,7 +6982,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -7008,7 +7020,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -7046,7 +7058,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -7084,7 +7096,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -7122,7 +7134,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -7160,7 +7172,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -7198,7 +7210,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -7236,7 +7248,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -7274,7 +7286,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -7312,7 +7324,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -7350,7 +7362,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -7388,7 +7400,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -7426,7 +7438,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -7464,7 +7476,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -7502,7 +7514,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -7540,7 +7552,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -7578,7 +7590,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -7616,7 +7628,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F95" s="1" t="s">
         <v>153</v>
       </c>
@@ -7636,7 +7648,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F96" s="1" t="s">
         <v>67</v>
       </c>
@@ -7659,7 +7671,7 @@
         <v>498.59999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -7697,7 +7709,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -7735,7 +7747,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -7773,7 +7785,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -7811,7 +7823,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -7849,7 +7861,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -7887,7 +7899,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -7925,7 +7937,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -7963,7 +7975,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -8001,7 +8013,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -8039,7 +8051,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -8077,7 +8089,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -8115,7 +8127,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -8153,7 +8165,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -8191,7 +8203,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -8229,7 +8241,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -8267,7 +8279,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>19</v>
       </c>
@@ -8305,7 +8317,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -8343,7 +8355,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -8381,7 +8393,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -8419,7 +8431,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -8457,7 +8469,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -8495,7 +8507,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -8533,7 +8545,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -8571,7 +8583,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -8609,7 +8621,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -8647,7 +8659,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -8685,7 +8697,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -8723,7 +8735,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -8761,7 +8773,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -8799,7 +8811,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -8837,7 +8849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -8875,7 +8887,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -8913,7 +8925,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -8951,7 +8963,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -8989,7 +9001,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -9027,7 +9039,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -9065,7 +9077,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -9103,7 +9115,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -9141,7 +9153,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -9179,7 +9191,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -9217,7 +9229,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -9255,7 +9267,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>19</v>
       </c>
@@ -9293,7 +9305,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>19</v>
       </c>
@@ -9331,7 +9343,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>19</v>
       </c>
@@ -9369,7 +9381,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>19</v>
       </c>
@@ -9407,7 +9419,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -9445,7 +9457,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>19</v>
       </c>
@@ -9483,7 +9495,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -9521,7 +9533,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -9559,7 +9571,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>19</v>
       </c>
@@ -9597,7 +9609,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>19</v>
       </c>
@@ -9635,7 +9647,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>19</v>
       </c>
@@ -9673,7 +9685,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -9711,7 +9723,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>19</v>
       </c>
@@ -9749,7 +9761,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -9787,7 +9799,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>19</v>
       </c>
@@ -9825,7 +9837,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>19</v>
       </c>
@@ -9863,7 +9875,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>19</v>
       </c>
@@ -9901,7 +9913,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>19</v>
       </c>
@@ -9939,7 +9951,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -9977,7 +9989,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>19</v>
       </c>
@@ -10015,7 +10027,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>19</v>
       </c>
@@ -10053,7 +10065,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>19</v>
       </c>
@@ -10091,7 +10103,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>19</v>
       </c>
@@ -10129,7 +10141,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -10167,7 +10179,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>19</v>
       </c>
@@ -10205,7 +10217,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -10243,7 +10255,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -10281,7 +10293,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -10319,7 +10331,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -10357,7 +10369,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>19</v>
       </c>
@@ -10395,7 +10407,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -10433,7 +10445,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
@@ -10471,7 +10483,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>19</v>
       </c>
@@ -10509,7 +10521,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>19</v>
       </c>
@@ -10547,7 +10559,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -10585,7 +10597,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>19</v>
       </c>
@@ -10623,7 +10635,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -10661,7 +10673,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>19</v>
       </c>
@@ -10699,7 +10711,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>19</v>
       </c>
@@ -10737,7 +10749,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>19</v>
       </c>
@@ -10775,7 +10787,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -10813,7 +10825,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>19</v>
       </c>
@@ -10851,7 +10863,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>19</v>
       </c>
@@ -10889,7 +10901,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -10927,7 +10939,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>19</v>
       </c>
@@ -10965,7 +10977,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>19</v>
       </c>
@@ -11003,7 +11015,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -11041,7 +11053,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>19</v>
       </c>
@@ -11079,7 +11091,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>19</v>
       </c>
@@ -11117,7 +11129,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>19</v>
       </c>
@@ -11155,7 +11167,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>19</v>
       </c>
@@ -11193,7 +11205,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>19</v>
       </c>
@@ -11231,7 +11243,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>19</v>
       </c>
@@ -11269,7 +11281,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>19</v>
       </c>
@@ -11307,7 +11319,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>19</v>
       </c>
@@ -11345,7 +11357,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>19</v>
       </c>
@@ -11383,7 +11395,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>19</v>
       </c>
@@ -11421,7 +11433,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>19</v>
       </c>
@@ -11459,7 +11471,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>19</v>
       </c>
@@ -11497,7 +11509,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>19</v>
       </c>
@@ -11535,7 +11547,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>19</v>
       </c>
@@ -11573,7 +11585,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>19</v>
       </c>
@@ -11611,7 +11623,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>19</v>
       </c>
@@ -11649,7 +11661,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>19</v>
       </c>
@@ -11687,7 +11699,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>19</v>
       </c>
@@ -11725,7 +11737,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>19</v>
       </c>
@@ -11763,7 +11775,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>19</v>
       </c>
@@ -11801,7 +11813,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>19</v>
       </c>
@@ -11839,7 +11851,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>19</v>
       </c>
@@ -11877,7 +11889,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>19</v>
       </c>
@@ -11915,7 +11927,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>19</v>
       </c>
@@ -11953,7 +11965,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>19</v>
       </c>
@@ -11991,7 +12003,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>19</v>
       </c>
@@ -12029,7 +12041,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>19</v>
       </c>
@@ -12067,7 +12079,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>19</v>
       </c>
@@ -12105,7 +12117,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -12143,7 +12155,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>19</v>
       </c>
@@ -12181,7 +12193,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>19</v>
       </c>
@@ -12219,7 +12231,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>19</v>
       </c>
@@ -12257,7 +12269,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>19</v>
       </c>
@@ -12295,7 +12307,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>19</v>
       </c>
@@ -12333,7 +12345,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>19</v>
       </c>
@@ -12371,7 +12383,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>19</v>
       </c>
@@ -12409,7 +12421,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>19</v>
       </c>
@@ -12447,7 +12459,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>19</v>
       </c>
@@ -12485,7 +12497,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>19</v>
       </c>
@@ -12523,7 +12535,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>19</v>
       </c>
@@ -12561,7 +12573,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>19</v>
       </c>
@@ -12599,7 +12611,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>19</v>
       </c>
@@ -12637,7 +12649,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>19</v>
       </c>
@@ -12675,7 +12687,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>19</v>
       </c>
@@ -12713,7 +12725,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>19</v>
       </c>
@@ -12751,7 +12763,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>19</v>
       </c>
@@ -12789,7 +12801,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>19</v>
       </c>
@@ -12827,7 +12839,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>19</v>
       </c>
@@ -12865,7 +12877,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>19</v>
       </c>
@@ -12903,7 +12915,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>19</v>
       </c>
@@ -12941,7 +12953,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>19</v>
       </c>
@@ -12979,7 +12991,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>19</v>
       </c>
@@ -13017,7 +13029,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>19</v>
       </c>
@@ -13055,7 +13067,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>19</v>
       </c>
@@ -13093,7 +13105,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>19</v>
       </c>
@@ -13131,7 +13143,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>19</v>
       </c>
@@ -13169,7 +13181,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -13207,7 +13219,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>19</v>
       </c>
@@ -13245,7 +13257,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>19</v>
       </c>
@@ -13283,7 +13295,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F245" s="1" t="s">
         <v>153</v>
       </c>
@@ -13303,7 +13315,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F246" s="1" t="s">
         <v>417</v>
       </c>
@@ -13323,7 +13335,7 @@
         <v>3431.3</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>19</v>
       </c>
@@ -13361,7 +13373,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>19</v>
       </c>
@@ -13399,7 +13411,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>19</v>
       </c>
@@ -13437,7 +13449,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>19</v>
       </c>
@@ -13475,7 +13487,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>19</v>
       </c>
@@ -13513,7 +13525,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>19</v>
       </c>
@@ -13551,7 +13563,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>19</v>
       </c>
@@ -13589,7 +13601,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>19</v>
       </c>
@@ -13627,7 +13639,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>19</v>
       </c>
@@ -13665,7 +13677,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>19</v>
       </c>
@@ -13703,7 +13715,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>19</v>
       </c>
@@ -13741,7 +13753,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>19</v>
       </c>
@@ -13779,7 +13791,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>19</v>
       </c>
@@ -13817,7 +13829,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>19</v>
       </c>
@@ -13855,7 +13867,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>19</v>
       </c>
@@ -13893,7 +13905,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>19</v>
       </c>
@@ -13931,7 +13943,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>19</v>
       </c>
@@ -13969,7 +13981,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>19</v>
       </c>
@@ -14007,7 +14019,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>19</v>
       </c>
@@ -14045,7 +14057,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>19</v>
       </c>
@@ -14083,7 +14095,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>19</v>
       </c>
@@ -14121,7 +14133,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>19</v>
       </c>
@@ -14159,7 +14171,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>19</v>
       </c>
@@ -14197,7 +14209,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>19</v>
       </c>
@@ -14235,7 +14247,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>19</v>
       </c>
@@ -14273,7 +14285,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>19</v>
       </c>
@@ -14311,7 +14323,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>19</v>
       </c>
@@ -14349,7 +14361,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>19</v>
       </c>
@@ -14387,7 +14399,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>19</v>
       </c>
@@ -14425,7 +14437,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>19</v>
       </c>
@@ -14463,7 +14475,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>19</v>
       </c>
@@ -14501,7 +14513,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>19</v>
       </c>
@@ -14539,7 +14551,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>19</v>
       </c>
@@ -14577,7 +14589,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>19</v>
       </c>
@@ -14615,7 +14627,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>19</v>
       </c>
@@ -14653,7 +14665,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>19</v>
       </c>
@@ -14691,7 +14703,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>19</v>
       </c>
@@ -14729,7 +14741,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>19</v>
       </c>
@@ -14767,7 +14779,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>19</v>
       </c>
@@ -14805,7 +14817,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>19</v>
       </c>
@@ -14843,7 +14855,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>19</v>
       </c>
@@ -14881,7 +14893,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>19</v>
       </c>
@@ -14919,7 +14931,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>19</v>
       </c>
@@ -14957,7 +14969,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>19</v>
       </c>
@@ -14995,7 +15007,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F291" s="1" t="s">
         <v>153</v>
       </c>
@@ -15015,7 +15027,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F292" s="1" t="s">
         <v>111</v>
       </c>
@@ -15035,7 +15047,7 @@
         <v>4430</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>19</v>
       </c>
@@ -15073,7 +15085,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>19</v>
       </c>
@@ -15111,7 +15123,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>19</v>
       </c>
@@ -15149,7 +15161,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>19</v>
       </c>
@@ -15187,7 +15199,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>19</v>
       </c>
@@ -15225,7 +15237,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>19</v>
       </c>
@@ -15263,7 +15275,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>19</v>
       </c>
@@ -15301,7 +15313,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>19</v>
       </c>
@@ -15339,7 +15351,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>19</v>
       </c>
@@ -15377,7 +15389,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>19</v>
       </c>
@@ -15415,7 +15427,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>19</v>
       </c>
@@ -15453,7 +15465,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>19</v>
       </c>
@@ -15491,7 +15503,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>19</v>
       </c>
@@ -15529,7 +15541,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>19</v>
       </c>
@@ -15567,7 +15579,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>19</v>
       </c>
@@ -15605,7 +15617,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>19</v>
       </c>
@@ -15643,7 +15655,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>19</v>
       </c>
@@ -15681,7 +15693,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>19</v>
       </c>
@@ -15719,7 +15731,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>19</v>
       </c>
@@ -15757,7 +15769,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>19</v>
       </c>
@@ -15795,7 +15807,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>19</v>
       </c>
@@ -15833,7 +15845,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>19</v>
       </c>
@@ -15871,7 +15883,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F315" s="1" t="s">
         <v>153</v>
       </c>
@@ -15891,7 +15903,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F316" s="1" t="s">
         <v>490</v>
       </c>
@@ -15911,7 +15923,7 @@
         <v>502.3</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>19</v>
       </c>
@@ -15949,7 +15961,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>19</v>
       </c>
@@ -15987,7 +15999,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>19</v>
       </c>
@@ -16025,7 +16037,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>19</v>
       </c>
@@ -16063,7 +16075,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>19</v>
       </c>
@@ -16101,7 +16113,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>19</v>
       </c>
@@ -16139,7 +16151,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>19</v>
       </c>
@@ -16177,7 +16189,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>19</v>
       </c>
@@ -16215,7 +16227,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>19</v>
       </c>
@@ -16253,7 +16265,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>19</v>
       </c>
@@ -16291,7 +16303,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>19</v>
       </c>
@@ -16329,7 +16341,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>19</v>
       </c>
@@ -16367,7 +16379,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>19</v>
       </c>
@@ -16405,7 +16417,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>19</v>
       </c>
@@ -16443,7 +16455,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>19</v>
       </c>
@@ -16481,7 +16493,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>19</v>
       </c>
@@ -16519,7 +16531,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>19</v>
       </c>
@@ -16557,7 +16569,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>19</v>
       </c>
@@ -16595,7 +16607,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>19</v>
       </c>
@@ -16633,7 +16645,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>19</v>
       </c>
@@ -16671,7 +16683,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>19</v>
       </c>
@@ -16709,7 +16721,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>19</v>
       </c>
@@ -16747,7 +16759,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>19</v>
       </c>
@@ -16785,7 +16797,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>19</v>
       </c>
@@ -16823,7 +16835,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>19</v>
       </c>
@@ -16861,7 +16873,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>19</v>
       </c>
@@ -16899,7 +16911,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>19</v>
       </c>
@@ -16937,7 +16949,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>19</v>
       </c>
@@ -16975,7 +16987,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>19</v>
       </c>
@@ -17013,7 +17025,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>19</v>
       </c>
@@ -17051,7 +17063,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>19</v>
       </c>
@@ -17089,7 +17101,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>19</v>
       </c>
@@ -17127,7 +17139,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>19</v>
       </c>
@@ -17165,7 +17177,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>19</v>
       </c>
@@ -17203,7 +17215,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>19</v>
       </c>
@@ -17241,7 +17253,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>19</v>
       </c>
@@ -17279,7 +17291,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>19</v>
       </c>
@@ -17317,7 +17329,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>19</v>
       </c>
@@ -17355,7 +17367,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>19</v>
       </c>
@@ -17393,7 +17405,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>19</v>
       </c>
@@ -17431,7 +17443,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>19</v>
       </c>
@@ -17469,7 +17481,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>19</v>
       </c>
@@ -17507,7 +17519,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>19</v>
       </c>
@@ -17545,7 +17557,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>19</v>
       </c>
@@ -17583,7 +17595,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>19</v>
       </c>
@@ -17621,7 +17633,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>19</v>
       </c>
@@ -17659,7 +17671,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>19</v>
       </c>
@@ -17697,7 +17709,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>19</v>
       </c>
@@ -17735,7 +17747,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>19</v>
       </c>
@@ -17773,7 +17785,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>19</v>
       </c>
@@ -17811,7 +17823,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>19</v>
       </c>
@@ -17849,7 +17861,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>19</v>
       </c>
@@ -17887,7 +17899,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>19</v>
       </c>
@@ -17925,7 +17937,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>19</v>
       </c>
@@ -17963,7 +17975,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>19</v>
       </c>
@@ -18001,7 +18013,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>19</v>
       </c>
@@ -18039,7 +18051,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>19</v>
       </c>
@@ -18077,7 +18089,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>19</v>
       </c>
@@ -18115,7 +18127,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>19</v>
       </c>
@@ -18153,7 +18165,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>19</v>
       </c>
@@ -18191,7 +18203,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>19</v>
       </c>
@@ -18229,7 +18241,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>19</v>
       </c>
@@ -18267,7 +18279,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>19</v>
       </c>
@@ -18305,7 +18317,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>19</v>
       </c>
@@ -18343,7 +18355,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>19</v>
       </c>
@@ -18381,7 +18393,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>19</v>
       </c>
@@ -18419,7 +18431,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>19</v>
       </c>
@@ -18457,7 +18469,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>19</v>
       </c>
@@ -18495,7 +18507,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>19</v>
       </c>
@@ -18533,7 +18545,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>19</v>
       </c>
@@ -18571,7 +18583,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>19</v>
       </c>
@@ -18609,7 +18621,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>19</v>
       </c>
@@ -18647,7 +18659,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>19</v>
       </c>
@@ -18685,7 +18697,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>19</v>
       </c>
@@ -18723,7 +18735,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>19</v>
       </c>
@@ -18761,7 +18773,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>19</v>
       </c>
@@ -18799,7 +18811,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>19</v>
       </c>
@@ -18837,7 +18849,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>19</v>
       </c>
@@ -18875,7 +18887,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>19</v>
       </c>
@@ -18913,7 +18925,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>19</v>
       </c>
@@ -18951,7 +18963,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>19</v>
       </c>
@@ -18989,7 +19001,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>19</v>
       </c>
@@ -19027,7 +19039,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>19</v>
       </c>
@@ -19065,7 +19077,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>19</v>
       </c>
@@ -19103,7 +19115,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>19</v>
       </c>
@@ -19141,7 +19153,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>19</v>
       </c>
@@ -19179,7 +19191,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>19</v>
       </c>
@@ -19217,7 +19229,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>19</v>
       </c>
@@ -19255,7 +19267,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>19</v>
       </c>
@@ -19293,7 +19305,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>19</v>
       </c>
@@ -19331,7 +19343,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>19</v>
       </c>
@@ -19369,7 +19381,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>19</v>
       </c>
@@ -19407,7 +19419,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>19</v>
       </c>
@@ -19445,7 +19457,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>19</v>
       </c>
@@ -19483,7 +19495,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>19</v>
       </c>
@@ -19521,7 +19533,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>19</v>
       </c>
@@ -19559,7 +19571,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>19</v>
       </c>
@@ -19597,7 +19609,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>19</v>
       </c>
@@ -19635,7 +19647,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>19</v>
       </c>
@@ -19673,7 +19685,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>19</v>
       </c>
@@ -19711,7 +19723,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>19</v>
       </c>
@@ -19749,7 +19761,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>19</v>
       </c>
@@ -19787,7 +19799,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>19</v>
       </c>
@@ -19825,7 +19837,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>19</v>
       </c>
@@ -19863,7 +19875,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>19</v>
       </c>
@@ -19901,7 +19913,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>19</v>
       </c>
@@ -19939,7 +19951,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>19</v>
       </c>
@@ -19977,7 +19989,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>19</v>
       </c>
@@ -20015,7 +20027,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>19</v>
       </c>
@@ -20053,7 +20065,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>19</v>
       </c>
@@ -20091,7 +20103,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>19</v>
       </c>
@@ -20129,7 +20141,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>19</v>
       </c>
@@ -20167,7 +20179,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>19</v>
       </c>
@@ -20205,7 +20217,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>19</v>
       </c>
@@ -20243,7 +20255,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>19</v>
       </c>
@@ -20281,7 +20293,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>19</v>
       </c>
@@ -20319,7 +20331,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>19</v>
       </c>
@@ -20357,7 +20369,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>19</v>
       </c>
@@ -20395,7 +20407,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>19</v>
       </c>
@@ -20433,7 +20445,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>19</v>
       </c>
@@ -20471,7 +20483,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>19</v>
       </c>
@@ -20509,7 +20521,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>19</v>
       </c>
@@ -20547,7 +20559,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>19</v>
       </c>
@@ -20585,7 +20597,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>19</v>
       </c>
@@ -20623,7 +20635,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>19</v>
       </c>
@@ -20661,7 +20673,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>19</v>
       </c>
@@ -20699,7 +20711,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>19</v>
       </c>
@@ -20737,7 +20749,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>19</v>
       </c>
@@ -20775,7 +20787,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>19</v>
       </c>
@@ -20813,7 +20825,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>19</v>
       </c>
@@ -20851,7 +20863,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>19</v>
       </c>
@@ -20889,7 +20901,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>19</v>
       </c>
@@ -20927,7 +20939,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>19</v>
       </c>
@@ -20965,7 +20977,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>19</v>
       </c>
@@ -21003,7 +21015,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>19</v>
       </c>
@@ -21041,7 +21053,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>19</v>
       </c>
@@ -21079,7 +21091,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>19</v>
       </c>
@@ -21117,7 +21129,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>19</v>
       </c>
@@ -21155,7 +21167,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>19</v>
       </c>
@@ -21193,7 +21205,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>19</v>
       </c>
@@ -21231,7 +21243,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>19</v>
       </c>
@@ -21269,7 +21281,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>19</v>
       </c>
@@ -21307,7 +21319,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>19</v>
       </c>
@@ -21345,7 +21357,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>19</v>
       </c>
@@ -21383,7 +21395,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
         <v>19</v>
       </c>
@@ -21421,7 +21433,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>19</v>
       </c>
@@ -21459,7 +21471,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>19</v>
       </c>
@@ -21497,7 +21509,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>19</v>
       </c>
@@ -21535,7 +21547,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>19</v>
       </c>
@@ -21573,7 +21585,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>19</v>
       </c>
@@ -21611,7 +21623,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>19</v>
       </c>
@@ -21649,7 +21661,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>19</v>
       </c>
@@ -21687,7 +21699,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>19</v>
       </c>
@@ -21725,7 +21737,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>19</v>
       </c>
@@ -21763,7 +21775,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>19</v>
       </c>
@@ -21801,7 +21813,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>19</v>
       </c>
@@ -21839,7 +21851,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>19</v>
       </c>
@@ -21877,7 +21889,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>19</v>
       </c>
@@ -21915,7 +21927,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>19</v>
       </c>
@@ -21953,7 +21965,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>19</v>
       </c>
@@ -21991,7 +22003,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>19</v>
       </c>
@@ -22029,7 +22041,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>19</v>
       </c>
@@ -22067,7 +22079,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>19</v>
       </c>
@@ -22105,7 +22117,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>19</v>
       </c>
@@ -22143,7 +22155,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>19</v>
       </c>
@@ -22181,7 +22193,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>19</v>
       </c>
@@ -22219,7 +22231,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>19</v>
       </c>
@@ -22257,7 +22269,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>19</v>
       </c>
@@ -22295,7 +22307,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>19</v>
       </c>
@@ -22333,7 +22345,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>19</v>
       </c>
@@ -22371,7 +22383,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>19</v>
       </c>
@@ -22409,7 +22421,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>19</v>
       </c>
@@ -22447,7 +22459,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F489" s="1" t="s">
         <v>153</v>
       </c>
@@ -22467,7 +22479,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F490" s="1" t="s">
         <v>688</v>
       </c>
@@ -22490,7 +22502,7 @@
         <v>3981.4999999999977</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>19</v>
       </c>
@@ -22528,7 +22540,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>19</v>
       </c>
@@ -22566,7 +22578,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>19</v>
       </c>
@@ -22604,7 +22616,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>19</v>
       </c>
@@ -22642,7 +22654,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>19</v>
       </c>
@@ -22680,7 +22692,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>19</v>
       </c>
@@ -22718,7 +22730,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>19</v>
       </c>
@@ -22756,7 +22768,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>19</v>
       </c>
@@ -22794,7 +22806,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>19</v>
       </c>
@@ -22832,7 +22844,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>19</v>
       </c>
@@ -22870,7 +22882,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>19</v>
       </c>
@@ -22908,7 +22920,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>19</v>
       </c>
@@ -22946,7 +22958,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
         <v>19</v>
       </c>
@@ -22984,7 +22996,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
         <v>19</v>
       </c>
@@ -23022,7 +23034,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>19</v>
       </c>
@@ -23060,7 +23072,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>19</v>
       </c>
@@ -23098,7 +23110,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>19</v>
       </c>
@@ -23136,7 +23148,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>19</v>
       </c>
@@ -23174,7 +23186,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>19</v>
       </c>
@@ -23212,7 +23224,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>19</v>
       </c>
@@ -23250,7 +23262,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>19</v>
       </c>
@@ -23288,7 +23300,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>19</v>
       </c>
@@ -23326,7 +23338,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>19</v>
       </c>
@@ -23364,7 +23376,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>19</v>
       </c>
@@ -23402,7 +23414,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>19</v>
       </c>
@@ -23440,7 +23452,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>19</v>
       </c>
@@ -23478,7 +23490,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>19</v>
       </c>
@@ -23516,7 +23528,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>19</v>
       </c>
@@ -23554,7 +23566,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>19</v>
       </c>
@@ -23592,7 +23604,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>19</v>
       </c>
@@ -23630,7 +23642,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>19</v>
       </c>
@@ -23668,7 +23680,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>19</v>
       </c>
@@ -23706,7 +23718,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>19</v>
       </c>
@@ -23744,7 +23756,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>19</v>
       </c>
@@ -23782,7 +23794,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>19</v>
       </c>
@@ -23820,7 +23832,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>19</v>
       </c>
@@ -23858,7 +23870,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>19</v>
       </c>
@@ -23896,7 +23908,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>19</v>
       </c>
@@ -23934,7 +23946,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>19</v>
       </c>
@@ -23972,7 +23984,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>19</v>
       </c>
@@ -24010,7 +24022,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>19</v>
       </c>
@@ -24048,7 +24060,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>19</v>
       </c>
@@ -24086,7 +24098,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>19</v>
       </c>
@@ -24124,7 +24136,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>19</v>
       </c>
@@ -24162,7 +24174,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>19</v>
       </c>
@@ -24200,7 +24212,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
         <v>19</v>
       </c>
@@ -24238,7 +24250,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
         <v>19</v>
       </c>
@@ -24276,7 +24288,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>19</v>
       </c>
@@ -24314,7 +24326,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
         <v>19</v>
       </c>
@@ -24352,7 +24364,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
         <v>19</v>
       </c>
@@ -24390,7 +24402,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
         <v>19</v>
       </c>
@@ -24428,7 +24440,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>19</v>
       </c>
@@ -24466,7 +24478,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
         <v>19</v>
       </c>
@@ -24504,7 +24516,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
         <v>19</v>
       </c>
@@ -24542,7 +24554,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>19</v>
       </c>
@@ -24580,7 +24592,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
         <v>19</v>
       </c>
@@ -24618,7 +24630,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
         <v>19</v>
       </c>
@@ -24656,7 +24668,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>19</v>
       </c>
@@ -24694,7 +24706,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>19</v>
       </c>
@@ -24732,7 +24744,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>19</v>
       </c>
@@ -24770,7 +24782,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>19</v>
       </c>
@@ -24808,7 +24820,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>19</v>
       </c>
@@ -24846,7 +24858,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="s">
         <v>19</v>
       </c>
@@ -24884,7 +24896,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>19</v>
       </c>
@@ -24922,7 +24934,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="s">
         <v>19</v>
       </c>
@@ -24960,7 +24972,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>19</v>
       </c>
@@ -24998,7 +25010,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>19</v>
       </c>
@@ -25036,7 +25048,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
         <v>19</v>
       </c>
@@ -25074,7 +25086,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" s="1" t="s">
         <v>19</v>
       </c>
@@ -25112,7 +25124,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>19</v>
       </c>
@@ -25150,7 +25162,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>19</v>
       </c>
@@ -25188,7 +25200,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>19</v>
       </c>
@@ -25226,7 +25238,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>19</v>
       </c>
@@ -25264,7 +25276,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>19</v>
       </c>
@@ -25302,7 +25314,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>19</v>
       </c>
@@ -25340,7 +25352,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>19</v>
       </c>
@@ -25378,7 +25390,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>19</v>
       </c>
@@ -25416,7 +25428,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>19</v>
       </c>
@@ -25454,7 +25466,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>19</v>
       </c>
@@ -25492,7 +25504,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>19</v>
       </c>
@@ -25530,7 +25542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>19</v>
       </c>
@@ -25568,7 +25580,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
         <v>19</v>
       </c>
@@ -25606,7 +25618,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>19</v>
       </c>
@@ -25644,7 +25656,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>19</v>
       </c>
@@ -25682,7 +25694,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>19</v>
       </c>
@@ -25720,7 +25732,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>19</v>
       </c>
@@ -25758,7 +25770,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>19</v>
       </c>
@@ -25796,7 +25808,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>19</v>
       </c>
@@ -25834,7 +25846,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>19</v>
       </c>
@@ -25872,7 +25884,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>19</v>
       </c>
@@ -25910,7 +25922,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>19</v>
       </c>
@@ -25948,7 +25960,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>19</v>
       </c>
@@ -25986,7 +25998,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="583" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>19</v>
       </c>
@@ -26024,7 +26036,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>19</v>
       </c>
@@ -26062,7 +26074,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>19</v>
       </c>
@@ -26100,7 +26112,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>19</v>
       </c>
@@ -26138,7 +26150,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>19</v>
       </c>
@@ -26176,7 +26188,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="588" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>19</v>
       </c>
@@ -26214,7 +26226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>19</v>
       </c>
@@ -26252,7 +26264,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>19</v>
       </c>
@@ -26290,7 +26302,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>19</v>
       </c>
@@ -26328,7 +26340,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
         <v>19</v>
       </c>
@@ -26366,7 +26378,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>19</v>
       </c>
@@ -26404,7 +26416,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>19</v>
       </c>
@@ -26442,7 +26454,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>19</v>
       </c>
@@ -26480,7 +26492,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>19</v>
       </c>
@@ -26518,7 +26530,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="s">
         <v>19</v>
       </c>
@@ -26556,7 +26568,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F598" s="1" t="s">
         <v>153</v>
       </c>
@@ -26576,7 +26588,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F599" s="1" t="s">
         <v>800</v>
       </c>
@@ -26596,7 +26608,7 @@
         <v>2463.6999999999998</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
         <v>19</v>
       </c>
@@ -26634,7 +26646,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>19</v>
       </c>
@@ -26672,7 +26684,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>19</v>
       </c>
@@ -26710,7 +26722,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="603" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="s">
         <v>19</v>
       </c>
@@ -26748,7 +26760,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>19</v>
       </c>
@@ -26786,7 +26798,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>19</v>
       </c>
@@ -26824,7 +26836,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
         <v>19</v>
       </c>
@@ -26862,7 +26874,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A607" s="1" t="s">
         <v>19</v>
       </c>
@@ -26900,7 +26912,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
         <v>19</v>
       </c>
@@ -26938,7 +26950,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="s">
         <v>19</v>
       </c>
@@ -26976,7 +26988,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
         <v>19</v>
       </c>
@@ -27014,7 +27026,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="s">
         <v>19</v>
       </c>
@@ -27052,7 +27064,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
         <v>19</v>
       </c>
@@ -27090,7 +27102,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="s">
         <v>19</v>
       </c>
@@ -27128,7 +27140,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
         <v>19</v>
       </c>
@@ -27166,7 +27178,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A615" s="1" t="s">
         <v>19</v>
       </c>
@@ -27204,7 +27216,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="616" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="s">
         <v>19</v>
       </c>
@@ -27242,7 +27254,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A617" s="1" t="s">
         <v>19</v>
       </c>
@@ -27280,7 +27292,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
         <v>19</v>
       </c>
@@ -27318,7 +27330,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A619" s="1" t="s">
         <v>19</v>
       </c>
@@ -27356,7 +27368,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
         <v>19</v>
       </c>
@@ -27394,7 +27406,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="621" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A621" s="1" t="s">
         <v>19</v>
       </c>
@@ -27432,7 +27444,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
         <v>19</v>
       </c>
@@ -27470,7 +27482,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="623" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A623" s="1" t="s">
         <v>19</v>
       </c>
@@ -27508,7 +27520,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
         <v>19</v>
       </c>
@@ -27546,7 +27558,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A625" s="1" t="s">
         <v>19</v>
       </c>
@@ -27584,7 +27596,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="626" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
         <v>19</v>
       </c>
@@ -27622,7 +27634,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="627" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A627" s="1" t="s">
         <v>19</v>
       </c>
@@ -27660,7 +27672,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
         <v>19</v>
       </c>
@@ -27698,7 +27710,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="s">
         <v>19</v>
       </c>
@@ -27736,7 +27748,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
         <v>19</v>
       </c>
@@ -27774,7 +27786,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A631" s="1" t="s">
         <v>19</v>
       </c>
@@ -27812,7 +27824,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
         <v>19</v>
       </c>
@@ -27850,7 +27862,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A633" s="1" t="s">
         <v>19</v>
       </c>
@@ -27888,7 +27900,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
         <v>19</v>
       </c>
@@ -27926,7 +27938,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="s">
         <v>19</v>
       </c>
@@ -27964,7 +27976,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
         <v>19</v>
       </c>
@@ -28002,7 +28014,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="s">
         <v>19</v>
       </c>
@@ -28040,7 +28052,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="638" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
         <v>19</v>
       </c>
@@ -28078,7 +28090,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A639" s="1" t="s">
         <v>19</v>
       </c>
@@ -28116,7 +28128,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="640" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="s">
         <v>19</v>
       </c>
@@ -28154,7 +28166,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" s="1" t="s">
         <v>19</v>
       </c>
@@ -28192,7 +28204,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="642" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
         <v>19</v>
       </c>
@@ -28230,7 +28242,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="643" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" s="1" t="s">
         <v>19</v>
       </c>
@@ -28268,7 +28280,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="s">
         <v>19</v>
       </c>
@@ -28306,7 +28318,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" s="1" t="s">
         <v>19</v>
       </c>
@@ -28344,7 +28356,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="s">
         <v>19</v>
       </c>
@@ -28382,7 +28394,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="647" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A647" s="1" t="s">
         <v>19</v>
       </c>
@@ -28420,7 +28432,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="648" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A648" s="1" t="s">
         <v>19</v>
       </c>
@@ -28458,7 +28470,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="649" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A649" s="1" t="s">
         <v>19</v>
       </c>
@@ -28496,7 +28508,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A650" s="1" t="s">
         <v>19</v>
       </c>
@@ -28534,7 +28546,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" s="1" t="s">
         <v>19</v>
       </c>
@@ -28572,7 +28584,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" s="1" t="s">
         <v>19</v>
       </c>
@@ -28610,7 +28622,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="653" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A653" s="1" t="s">
         <v>19</v>
       </c>
@@ -28648,7 +28660,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="654" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A654" s="1" t="s">
         <v>19</v>
       </c>
@@ -28686,7 +28698,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" s="1" t="s">
         <v>19</v>
       </c>
@@ -28724,7 +28736,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="656" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A656" s="1" t="s">
         <v>19</v>
       </c>
@@ -28762,7 +28774,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" s="1" t="s">
         <v>19</v>
       </c>
@@ -28800,7 +28812,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="658" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A658" s="1" t="s">
         <v>19</v>
       </c>
@@ -28838,7 +28850,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="659" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A659" s="1" t="s">
         <v>19</v>
       </c>
@@ -28876,7 +28888,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="660" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A660" s="1" t="s">
         <v>19</v>
       </c>
@@ -28914,7 +28926,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" s="1" t="s">
         <v>19</v>
       </c>
@@ -28952,7 +28964,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="662" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A662" s="1" t="s">
         <v>19</v>
       </c>
@@ -28990,7 +29002,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="663" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" s="1" t="s">
         <v>19</v>
       </c>
@@ -29028,7 +29040,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="s">
         <v>19</v>
       </c>
@@ -29066,7 +29078,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A665" s="1" t="s">
         <v>19</v>
       </c>
@@ -29104,7 +29116,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="s">
         <v>19</v>
       </c>
@@ -29142,7 +29154,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" s="1" t="s">
         <v>19</v>
       </c>
@@ -29180,7 +29192,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="668" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A668" s="1" t="s">
         <v>19</v>
       </c>
@@ -29218,7 +29230,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" s="1" t="s">
         <v>19</v>
       </c>
@@ -29256,7 +29268,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="s">
         <v>19</v>
       </c>
@@ -29294,7 +29306,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" s="1" t="s">
         <v>19</v>
       </c>
@@ -29332,7 +29344,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="672" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A672" s="1" t="s">
         <v>19</v>
       </c>
@@ -29370,7 +29382,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="673" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" s="1" t="s">
         <v>19</v>
       </c>
@@ -29408,7 +29420,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="s">
         <v>19</v>
       </c>
@@ -29446,7 +29458,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" s="1" t="s">
         <v>19</v>
       </c>
@@ -29484,7 +29496,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="s">
         <v>19</v>
       </c>
@@ -29522,7 +29534,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" s="1" t="s">
         <v>19</v>
       </c>
@@ -29560,7 +29572,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="678" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" s="1" t="s">
         <v>19</v>
       </c>
@@ -29598,7 +29610,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" s="1" t="s">
         <v>19</v>
       </c>
@@ -29636,7 +29648,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A680" s="1" t="s">
         <v>19</v>
       </c>
@@ -29674,7 +29686,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="681" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A681" s="1" t="s">
         <v>19</v>
       </c>
@@ -29712,7 +29724,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="682" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A682" s="1" t="s">
         <v>19</v>
       </c>
@@ -29750,7 +29762,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="683" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A683" s="1" t="s">
         <v>19</v>
       </c>
@@ -29788,7 +29800,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A684" s="1" t="s">
         <v>19</v>
       </c>
@@ -29826,7 +29838,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="685" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A685" s="1" t="s">
         <v>19</v>
       </c>
@@ -29864,7 +29876,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A686" s="1" t="s">
         <v>19</v>
       </c>
@@ -29902,7 +29914,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A687" s="1" t="s">
         <v>19</v>
       </c>
@@ -29940,7 +29952,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="688" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A688" s="1" t="s">
         <v>19</v>
       </c>
@@ -29978,7 +29990,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A689" s="1" t="s">
         <v>19</v>
       </c>
@@ -30016,7 +30028,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A690" s="1" t="s">
         <v>19</v>
       </c>
@@ -30054,7 +30066,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="691" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A691" s="1" t="s">
         <v>19</v>
       </c>
@@ -30092,7 +30104,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A692" s="1" t="s">
         <v>19</v>
       </c>
@@ -30130,7 +30142,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="693" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A693" s="1" t="s">
         <v>19</v>
       </c>
@@ -30168,7 +30180,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="694" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A694" s="1" t="s">
         <v>19</v>
       </c>
@@ -30206,7 +30218,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="695" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A695" s="1" t="s">
         <v>19</v>
       </c>
@@ -30244,7 +30256,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A696" s="1" t="s">
         <v>19</v>
       </c>
@@ -30282,7 +30294,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="697" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A697" s="1" t="s">
         <v>19</v>
       </c>
@@ -30320,7 +30332,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="698" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A698" s="1" t="s">
         <v>19</v>
       </c>
@@ -30358,7 +30370,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A699" s="1" t="s">
         <v>19</v>
       </c>
@@ -30396,7 +30408,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="700" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A700" s="1" t="s">
         <v>19</v>
       </c>
@@ -30434,7 +30446,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A701" s="1" t="s">
         <v>19</v>
       </c>
@@ -30472,7 +30484,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A702" s="1" t="s">
         <v>19</v>
       </c>
@@ -30510,7 +30522,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="703" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A703" s="1" t="s">
         <v>19</v>
       </c>
@@ -30548,7 +30560,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="704" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A704" s="1" t="s">
         <v>19</v>
       </c>
@@ -30586,7 +30598,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A705" s="1" t="s">
         <v>19</v>
       </c>
@@ -30624,7 +30636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A706" s="1" t="s">
         <v>19</v>
       </c>
@@ -30662,7 +30674,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A707" s="1" t="s">
         <v>19</v>
       </c>
@@ -30700,7 +30712,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="708" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A708" s="1" t="s">
         <v>19</v>
       </c>
@@ -30738,7 +30750,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A709" s="1" t="s">
         <v>19</v>
       </c>
@@ -30776,7 +30788,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A710" s="1" t="s">
         <v>19</v>
       </c>
@@ -30814,7 +30826,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A711" s="1" t="s">
         <v>19</v>
       </c>
@@ -30852,7 +30864,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A712" s="1" t="s">
         <v>19</v>
       </c>
@@ -30890,7 +30902,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A713" s="1" t="s">
         <v>19</v>
       </c>
@@ -30928,7 +30940,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A714" s="1" t="s">
         <v>19</v>
       </c>
@@ -30966,7 +30978,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A715" s="1" t="s">
         <v>19</v>
       </c>
@@ -31004,7 +31016,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A716" s="1" t="s">
         <v>19</v>
       </c>
@@ -31042,7 +31054,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="717" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A717" s="1" t="s">
         <v>19</v>
       </c>
@@ -31080,7 +31092,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A718" s="1" t="s">
         <v>19</v>
       </c>
@@ -31118,7 +31130,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="719" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A719" s="1" t="s">
         <v>19</v>
       </c>
@@ -31156,7 +31168,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A720" s="1" t="s">
         <v>19</v>
       </c>
@@ -31194,7 +31206,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="721" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A721" s="1" t="s">
         <v>19</v>
       </c>
@@ -31232,7 +31244,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="722" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A722" s="1" t="s">
         <v>19</v>
       </c>
@@ -31270,7 +31282,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="723" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A723" s="1" t="s">
         <v>19</v>
       </c>
@@ -31308,7 +31320,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="724" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A724" s="1" t="s">
         <v>19</v>
       </c>
@@ -31346,7 +31358,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="725" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A725" s="1" t="s">
         <v>19</v>
       </c>
@@ -31384,7 +31396,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="726" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A726" s="1" t="s">
         <v>19</v>
       </c>
@@ -31422,7 +31434,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="727" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A727" s="1" t="s">
         <v>19</v>
       </c>
@@ -31460,7 +31472,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="728" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A728" s="1" t="s">
         <v>19</v>
       </c>
@@ -31498,7 +31510,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="729" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A729" s="1" t="s">
         <v>19</v>
       </c>
@@ -31536,7 +31548,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="730" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A730" s="1" t="s">
         <v>19</v>
       </c>
@@ -31574,7 +31586,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="731" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A731" s="1" t="s">
         <v>19</v>
       </c>
@@ -31612,7 +31624,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="732" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A732" s="1" t="s">
         <v>19</v>
       </c>
@@ -31650,7 +31662,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="733" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A733" s="1" t="s">
         <v>19</v>
       </c>
@@ -31688,7 +31700,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="734" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A734" s="1" t="s">
         <v>19</v>
       </c>
@@ -31726,7 +31738,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A735" s="1" t="s">
         <v>19</v>
       </c>
@@ -31764,7 +31776,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A736" s="1" t="s">
         <v>19</v>
       </c>
@@ -31802,7 +31814,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="737" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A737" s="1" t="s">
         <v>19</v>
       </c>
@@ -31840,7 +31852,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="738" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A738" s="1" t="s">
         <v>19</v>
       </c>
@@ -31878,7 +31890,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="739" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A739" s="1" t="s">
         <v>19</v>
       </c>
@@ -31916,7 +31928,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="740" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A740" s="1" t="s">
         <v>19</v>
       </c>
@@ -31954,7 +31966,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="741" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A741" s="1" t="s">
         <v>19</v>
       </c>
@@ -31992,7 +32004,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="742" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A742" s="1" t="s">
         <v>19</v>
       </c>
@@ -32030,7 +32042,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="743" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A743" s="1" t="s">
         <v>19</v>
       </c>
@@ -32068,7 +32080,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="744" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A744" s="1" t="s">
         <v>19</v>
       </c>
@@ -32106,7 +32118,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="745" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A745" s="1" t="s">
         <v>19</v>
       </c>
@@ -32144,7 +32156,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A746" s="1" t="s">
         <v>19</v>
       </c>
@@ -32182,7 +32194,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="747" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A747" s="1" t="s">
         <v>19</v>
       </c>
@@ -32220,7 +32232,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="748" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A748" s="1" t="s">
         <v>19</v>
       </c>
@@ -32258,7 +32270,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="749" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A749" s="1" t="s">
         <v>19</v>
       </c>
@@ -32296,7 +32308,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="750" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A750" s="1" t="s">
         <v>19</v>
       </c>
@@ -32334,7 +32346,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="751" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A751" s="1" t="s">
         <v>19</v>
       </c>
@@ -32372,7 +32384,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="752" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A752" s="1" t="s">
         <v>19</v>
       </c>
@@ -32410,7 +32422,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="753" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A753" s="1" t="s">
         <v>19</v>
       </c>
@@ -32448,7 +32460,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="754" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A754" s="1" t="s">
         <v>19</v>
       </c>
@@ -32486,7 +32498,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="755" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A755" s="1" t="s">
         <v>19</v>
       </c>
@@ -32524,7 +32536,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="756" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A756" s="1" t="s">
         <v>19</v>
       </c>
@@ -32562,7 +32574,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="757" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A757" s="1" t="s">
         <v>19</v>
       </c>
@@ -32600,7 +32612,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A758" s="1" t="s">
         <v>19</v>
       </c>
@@ -32638,7 +32650,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="759" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A759" s="1" t="s">
         <v>19</v>
       </c>
@@ -32676,7 +32688,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="760" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A760" s="1" t="s">
         <v>19</v>
       </c>
@@ -32714,7 +32726,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="761" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A761" s="1" t="s">
         <v>19</v>
       </c>
@@ -32752,7 +32764,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="762" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A762" s="1" t="s">
         <v>19</v>
       </c>
@@ -32790,7 +32802,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="763" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A763" s="1" t="s">
         <v>19</v>
       </c>
@@ -32828,7 +32840,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="764" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A764" s="1" t="s">
         <v>19</v>
       </c>
@@ -32866,7 +32878,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="765" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A765" s="1" t="s">
         <v>19</v>
       </c>
@@ -32904,7 +32916,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="766" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A766" s="1" t="s">
         <v>19</v>
       </c>
@@ -32942,7 +32954,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="767" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A767" s="1" t="s">
         <v>19</v>
       </c>
@@ -32980,7 +32992,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="768" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A768" s="1" t="s">
         <v>19</v>
       </c>
@@ -33018,7 +33030,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="769" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A769" s="1" t="s">
         <v>19</v>
       </c>
@@ -33056,7 +33068,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="770" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A770" s="1" t="s">
         <v>19</v>
       </c>
@@ -33094,7 +33106,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A771" s="1" t="s">
         <v>19</v>
       </c>
@@ -33132,7 +33144,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="772" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A772" s="1" t="s">
         <v>19</v>
       </c>
@@ -33170,7 +33182,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="773" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A773" s="1" t="s">
         <v>19</v>
       </c>
@@ -33208,7 +33220,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="774" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A774" s="1" t="s">
         <v>19</v>
       </c>
@@ -33246,7 +33258,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="775" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A775" s="1" t="s">
         <v>19</v>
       </c>
@@ -33284,7 +33296,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="776" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A776" s="1" t="s">
         <v>19</v>
       </c>
@@ -33322,7 +33334,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="777" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A777" s="1" t="s">
         <v>19</v>
       </c>
@@ -33360,7 +33372,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="778" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A778" s="1" t="s">
         <v>19</v>
       </c>
@@ -33398,7 +33410,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="779" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A779" s="1" t="s">
         <v>19</v>
       </c>
@@ -33436,7 +33448,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="780" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A780" s="1" t="s">
         <v>19</v>
       </c>
@@ -33474,7 +33486,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="781" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A781" s="1" t="s">
         <v>19</v>
       </c>
@@ -33512,7 +33524,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="782" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A782" s="1" t="s">
         <v>19</v>
       </c>
@@ -33550,7 +33562,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="783" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A783" s="1" t="s">
         <v>19</v>
       </c>
@@ -33588,7 +33600,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="784" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A784" s="1" t="s">
         <v>19</v>
       </c>
@@ -33626,7 +33638,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="785" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A785" s="1" t="s">
         <v>19</v>
       </c>
@@ -33664,7 +33676,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="786" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A786" s="1" t="s">
         <v>19</v>
       </c>
@@ -33702,7 +33714,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="787" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A787" s="1" t="s">
         <v>19</v>
       </c>
@@ -33740,7 +33752,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="788" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A788" s="1" t="s">
         <v>19</v>
       </c>
@@ -33778,7 +33790,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="789" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A789" s="1" t="s">
         <v>19</v>
       </c>
@@ -33816,7 +33828,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="790" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A790" s="1" t="s">
         <v>19</v>
       </c>
@@ -33854,7 +33866,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="791" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A791" s="1" t="s">
         <v>19</v>
       </c>
@@ -33892,7 +33904,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="792" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A792" s="1" t="s">
         <v>19</v>
       </c>
@@ -33930,7 +33942,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="793" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A793" s="1" t="s">
         <v>19</v>
       </c>
@@ -33968,7 +33980,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="794" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A794" s="1" t="s">
         <v>19</v>
       </c>
@@ -34006,7 +34018,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="795" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A795" s="1" t="s">
         <v>19</v>
       </c>
@@ -34044,7 +34056,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="796" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A796" s="1" t="s">
         <v>19</v>
       </c>
@@ -34082,7 +34094,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="797" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A797" s="1" t="s">
         <v>19</v>
       </c>
@@ -34120,7 +34132,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="798" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A798" s="1" t="s">
         <v>19</v>
       </c>
@@ -34158,7 +34170,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="799" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A799" s="1" t="s">
         <v>19</v>
       </c>
@@ -34196,7 +34208,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="800" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A800" s="1" t="s">
         <v>19</v>
       </c>
@@ -34234,7 +34246,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="801" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A801" s="1" t="s">
         <v>19</v>
       </c>
@@ -34272,7 +34284,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="802" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A802" s="1" t="s">
         <v>19</v>
       </c>
@@ -34310,7 +34322,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="803" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A803" s="1" t="s">
         <v>19</v>
       </c>
@@ -34348,7 +34360,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="804" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A804" s="1" t="s">
         <v>19</v>
       </c>
@@ -34386,7 +34398,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="805" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A805" s="1" t="s">
         <v>19</v>
       </c>
@@ -34424,7 +34436,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="806" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A806" s="1" t="s">
         <v>19</v>
       </c>
@@ -34462,7 +34474,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="807" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A807" s="1" t="s">
         <v>19</v>
       </c>
@@ -34500,7 +34512,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="808" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A808" s="1" t="s">
         <v>19</v>
       </c>
@@ -34538,7 +34550,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="809" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A809" s="1" t="s">
         <v>19</v>
       </c>
@@ -34576,7 +34588,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="810" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A810" s="1" t="s">
         <v>19</v>
       </c>
@@ -34614,7 +34626,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="811" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A811" s="1" t="s">
         <v>19</v>
       </c>
@@ -34652,7 +34664,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="812" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A812" s="1" t="s">
         <v>19</v>
       </c>
@@ -34690,7 +34702,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="813" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A813" s="1" t="s">
         <v>19</v>
       </c>
@@ -34728,7 +34740,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="814" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A814" s="1" t="s">
         <v>19</v>
       </c>
@@ -34766,7 +34778,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="815" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A815" s="1" t="s">
         <v>19</v>
       </c>
@@ -34804,7 +34816,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="816" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A816" s="1" t="s">
         <v>19</v>
       </c>
@@ -34842,7 +34854,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="817" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A817" s="1" t="s">
         <v>19</v>
       </c>
@@ -34880,7 +34892,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="818" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A818" s="1" t="s">
         <v>19</v>
       </c>
@@ -34918,7 +34930,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="819" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A819" s="1" t="s">
         <v>19</v>
       </c>
@@ -34956,7 +34968,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="820" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A820" s="1" t="s">
         <v>19</v>
       </c>
@@ -34994,7 +35006,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="821" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A821" s="1" t="s">
         <v>19</v>
       </c>
@@ -35032,7 +35044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="822" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A822" s="1" t="s">
         <v>19</v>
       </c>
@@ -35070,7 +35082,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="823" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A823" s="1" t="s">
         <v>19</v>
       </c>
@@ -35108,7 +35120,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="824" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A824" s="1" t="s">
         <v>19</v>
       </c>
@@ -35146,7 +35158,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="825" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A825" s="1" t="s">
         <v>19</v>
       </c>
@@ -35184,7 +35196,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="826" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A826" s="1" t="s">
         <v>19</v>
       </c>
@@ -35222,7 +35234,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="827" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A827" s="1" t="s">
         <v>19</v>
       </c>
@@ -35260,7 +35272,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="828" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A828" s="1" t="s">
         <v>19</v>
       </c>
@@ -35298,7 +35310,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="829" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A829" s="1" t="s">
         <v>19</v>
       </c>
@@ -35336,7 +35348,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="830" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A830" s="1" t="s">
         <v>19</v>
       </c>
@@ -35374,7 +35386,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="831" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A831" s="1" t="s">
         <v>19</v>
       </c>
@@ -35412,7 +35424,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="832" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A832" s="1" t="s">
         <v>19</v>
       </c>
@@ -35450,7 +35462,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="833" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A833" s="1" t="s">
         <v>19</v>
       </c>
@@ -35488,7 +35500,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="834" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A834" s="1" t="s">
         <v>19</v>
       </c>
@@ -35526,7 +35538,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="835" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A835" s="1" t="s">
         <v>19</v>
       </c>
@@ -35564,7 +35576,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="836" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A836" s="1" t="s">
         <v>19</v>
       </c>
@@ -35602,7 +35614,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="837" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A837" s="1" t="s">
         <v>19</v>
       </c>
@@ -35640,7 +35652,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="838" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A838" s="1" t="s">
         <v>19</v>
       </c>
@@ -35678,7 +35690,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="839" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A839" s="1" t="s">
         <v>19</v>
       </c>
@@ -35716,7 +35728,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="840" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A840" s="1" t="s">
         <v>19</v>
       </c>
@@ -35754,7 +35766,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="841" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A841" s="1" t="s">
         <v>19</v>
       </c>
@@ -35792,7 +35804,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="842" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A842" s="1" t="s">
         <v>19</v>
       </c>
@@ -35830,7 +35842,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="843" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A843" s="1" t="s">
         <v>19</v>
       </c>
@@ -35868,7 +35880,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="844" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A844" s="1" t="s">
         <v>19</v>
       </c>
@@ -35906,7 +35918,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="845" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A845" s="1" t="s">
         <v>19</v>
       </c>
@@ -35944,7 +35956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="846" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A846" s="1" t="s">
         <v>19</v>
       </c>
@@ -35982,7 +35994,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="847" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A847" s="1" t="s">
         <v>19</v>
       </c>
@@ -36020,7 +36032,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="848" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A848" s="1" t="s">
         <v>19</v>
       </c>
@@ -36058,7 +36070,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="849" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A849" s="1" t="s">
         <v>19</v>
       </c>
@@ -36096,7 +36108,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="850" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A850" s="1" t="s">
         <v>19</v>
       </c>
@@ -36134,7 +36146,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="851" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A851" s="1" t="s">
         <v>19</v>
       </c>
@@ -36172,7 +36184,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="852" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A852" s="1" t="s">
         <v>19</v>
       </c>
@@ -36210,7 +36222,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="853" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A853" s="1" t="s">
         <v>19</v>
       </c>
@@ -36248,7 +36260,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="854" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A854" s="1" t="s">
         <v>19</v>
       </c>
@@ -36286,7 +36298,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="855" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A855" s="1" t="s">
         <v>19</v>
       </c>
@@ -36324,7 +36336,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="856" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A856" s="1" t="s">
         <v>19</v>
       </c>
@@ -36362,7 +36374,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="857" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A857" s="1" t="s">
         <v>19</v>
       </c>
@@ -36400,7 +36412,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="858" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A858" s="1" t="s">
         <v>19</v>
       </c>
@@ -36438,7 +36450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="859" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A859" s="1" t="s">
         <v>19</v>
       </c>
@@ -36476,7 +36488,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="860" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A860" s="1" t="s">
         <v>19</v>
       </c>
@@ -36514,7 +36526,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="861" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A861" s="1" t="s">
         <v>19</v>
       </c>
@@ -36552,7 +36564,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="862" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A862" s="1" t="s">
         <v>19</v>
       </c>
@@ -36590,7 +36602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="863" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A863" s="1" t="s">
         <v>19</v>
       </c>
@@ -36628,7 +36640,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="864" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A864" s="1" t="s">
         <v>19</v>
       </c>
@@ -36666,7 +36678,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="865" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A865" s="1" t="s">
         <v>19</v>
       </c>
@@ -36704,7 +36716,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="866" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A866" s="1" t="s">
         <v>19</v>
       </c>
@@ -36742,7 +36754,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="867" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A867" s="1" t="s">
         <v>19</v>
       </c>
@@ -36780,7 +36792,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="868" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A868" s="1" t="s">
         <v>19</v>
       </c>
@@ -36818,7 +36830,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="869" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A869" s="1" t="s">
         <v>19</v>
       </c>
@@ -36856,7 +36868,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="870" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A870" s="1" t="s">
         <v>19</v>
       </c>
@@ -36894,7 +36906,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="871" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A871" s="1" t="s">
         <v>19</v>
       </c>
@@ -36932,7 +36944,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="872" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A872" s="1" t="s">
         <v>19</v>
       </c>
@@ -36970,7 +36982,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="873" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A873" s="1" t="s">
         <v>19</v>
       </c>
@@ -37008,7 +37020,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="874" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A874" s="1" t="s">
         <v>19</v>
       </c>
@@ -37046,7 +37058,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="875" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F875" s="1" t="s">
         <v>153</v>
       </c>
@@ -37066,7 +37078,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="876" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F876" s="1" t="s">
         <v>1179</v>
       </c>
@@ -37083,7 +37095,7 @@
         <v>6454.7999999999984</v>
       </c>
     </row>
-    <row r="877" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A877" s="1" t="s">
         <v>19</v>
       </c>
@@ -37121,7 +37133,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="878" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A878" s="1" t="s">
         <v>19</v>
       </c>
@@ -37159,7 +37171,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="879" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A879" s="1" t="s">
         <v>19</v>
       </c>
@@ -37197,7 +37209,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="880" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A880" s="1" t="s">
         <v>19</v>
       </c>
@@ -37235,7 +37247,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="881" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A881" s="1" t="s">
         <v>19</v>
       </c>
@@ -37273,7 +37285,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="882" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A882" s="1" t="s">
         <v>19</v>
       </c>
@@ -37311,7 +37323,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="883" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A883" s="1" t="s">
         <v>19</v>
       </c>
@@ -37349,7 +37361,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="884" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A884" s="1" t="s">
         <v>19</v>
       </c>
@@ -37387,7 +37399,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="885" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A885" s="1" t="s">
         <v>19</v>
       </c>
@@ -37425,7 +37437,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="886" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A886" s="1" t="s">
         <v>19</v>
       </c>
@@ -37463,7 +37475,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="887" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A887" s="1" t="s">
         <v>19</v>
       </c>
@@ -37501,7 +37513,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="888" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A888" s="1" t="s">
         <v>19</v>
       </c>
@@ -37539,7 +37551,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="889" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A889" s="1" t="s">
         <v>19</v>
       </c>
@@ -37577,7 +37589,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="890" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A890" s="1" t="s">
         <v>19</v>
       </c>
@@ -37615,7 +37627,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="891" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A891" s="1" t="s">
         <v>19</v>
       </c>
@@ -37653,7 +37665,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="892" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A892" s="1" t="s">
         <v>19</v>
       </c>
@@ -37691,7 +37703,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="893" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A893" s="1" t="s">
         <v>19</v>
       </c>
@@ -37729,7 +37741,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="894" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A894" s="1" t="s">
         <v>19</v>
       </c>
@@ -37767,7 +37779,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="895" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A895" s="1" t="s">
         <v>19</v>
       </c>
@@ -37805,7 +37817,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="896" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A896" s="1" t="s">
         <v>19</v>
       </c>
@@ -37843,7 +37855,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="897" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A897" s="1" t="s">
         <v>19</v>
       </c>
@@ -37881,7 +37893,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="898" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A898" s="1" t="s">
         <v>19</v>
       </c>
@@ -37919,7 +37931,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="899" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A899" s="1" t="s">
         <v>19</v>
       </c>
@@ -37957,7 +37969,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="900" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A900" s="1" t="s">
         <v>19</v>
       </c>
@@ -37995,7 +38007,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="901" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A901" s="1" t="s">
         <v>19</v>
       </c>
@@ -38033,7 +38045,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="902" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A902" s="1" t="s">
         <v>19</v>
       </c>
@@ -38071,7 +38083,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="903" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A903" s="1" t="s">
         <v>19</v>
       </c>
@@ -38109,7 +38121,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="904" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A904" s="1" t="s">
         <v>19</v>
       </c>
@@ -38147,7 +38159,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="905" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A905" s="1" t="s">
         <v>19</v>
       </c>
@@ -38185,7 +38197,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="906" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A906" s="1" t="s">
         <v>19</v>
       </c>
@@ -38223,7 +38235,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="907" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A907" s="1" t="s">
         <v>19</v>
       </c>
@@ -38261,7 +38273,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="908" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A908" s="1" t="s">
         <v>19</v>
       </c>
@@ -38299,7 +38311,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="909" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A909" s="1" t="s">
         <v>19</v>
       </c>
@@ -38337,7 +38349,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="910" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A910" s="1" t="s">
         <v>19</v>
       </c>
@@ -38375,7 +38387,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="911" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A911" s="1" t="s">
         <v>19</v>
       </c>
@@ -38413,7 +38425,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="912" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A912" s="1" t="s">
         <v>19</v>
       </c>
@@ -38451,7 +38463,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="913" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A913" s="1" t="s">
         <v>19</v>
       </c>
@@ -38489,7 +38501,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="914" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A914" s="1" t="s">
         <v>19</v>
       </c>
@@ -38527,7 +38539,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="915" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A915" s="1" t="s">
         <v>19</v>
       </c>
@@ -38565,7 +38577,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="916" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A916" s="1" t="s">
         <v>19</v>
       </c>
@@ -38603,7 +38615,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="917" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A917" s="1" t="s">
         <v>19</v>
       </c>
@@ -38641,7 +38653,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="918" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A918" s="1" t="s">
         <v>19</v>
       </c>
@@ -38679,7 +38691,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="919" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A919" s="1" t="s">
         <v>19</v>
       </c>
@@ -38717,7 +38729,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="920" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A920" s="1" t="s">
         <v>19</v>
       </c>
@@ -38755,7 +38767,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="921" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F921" s="1" t="s">
         <v>153</v>
       </c>
@@ -38775,7 +38787,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="922" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F922" s="1" t="s">
         <v>1228</v>
       </c>
@@ -38795,7 +38807,7 @@
         <v>1041.3</v>
       </c>
     </row>
-    <row r="923" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A923" s="1" t="s">
         <v>19</v>
       </c>
@@ -38833,7 +38845,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="924" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A924" s="1" t="s">
         <v>19</v>
       </c>
@@ -38871,7 +38883,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="925" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A925" s="1" t="s">
         <v>19</v>
       </c>
@@ -38909,7 +38921,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="926" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A926" s="1" t="s">
         <v>19</v>
       </c>
@@ -38947,7 +38959,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="927" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A927" s="1" t="s">
         <v>19</v>
       </c>
@@ -38985,7 +38997,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="928" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A928" s="1" t="s">
         <v>19</v>
       </c>
@@ -39023,7 +39035,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="929" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A929" s="1" t="s">
         <v>19</v>
       </c>
@@ -39061,7 +39073,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="930" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A930" s="1" t="s">
         <v>19</v>
       </c>
@@ -39099,7 +39111,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="931" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A931" s="1" t="s">
         <v>19</v>
       </c>
@@ -39137,7 +39149,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="932" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A932" s="1" t="s">
         <v>19</v>
       </c>
@@ -39175,7 +39187,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="933" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A933" s="1" t="s">
         <v>19</v>
       </c>
@@ -39213,7 +39225,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="934" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A934" s="1" t="s">
         <v>19</v>
       </c>
@@ -39251,7 +39263,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="935" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A935" s="1" t="s">
         <v>19</v>
       </c>
@@ -39289,7 +39301,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="936" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A936" s="1" t="s">
         <v>19</v>
       </c>
@@ -39327,7 +39339,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="937" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A937" s="1" t="s">
         <v>19</v>
       </c>
@@ -39365,7 +39377,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="938" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A938" s="1" t="s">
         <v>19</v>
       </c>
@@ -39403,7 +39415,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="939" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A939" s="1" t="s">
         <v>19</v>
       </c>
@@ -39441,7 +39453,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="940" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A940" s="1" t="s">
         <v>19</v>
       </c>
@@ -39479,7 +39491,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="941" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A941" s="1" t="s">
         <v>19</v>
       </c>
@@ -39517,7 +39529,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="942" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A942" s="1" t="s">
         <v>19</v>
       </c>
@@ -39555,7 +39567,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="943" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A943" s="1" t="s">
         <v>19</v>
       </c>
@@ -39593,7 +39605,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="944" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A944" s="1" t="s">
         <v>19</v>
       </c>
@@ -39631,7 +39643,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="945" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A945" s="1" t="s">
         <v>19</v>
       </c>
@@ -39669,7 +39681,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="946" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A946" s="1" t="s">
         <v>19</v>
       </c>
@@ -39707,7 +39719,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="947" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A947" s="1" t="s">
         <v>19</v>
       </c>
@@ -39745,7 +39757,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="948" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A948" s="1" t="s">
         <v>19</v>
       </c>
@@ -39783,7 +39795,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="949" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A949" s="1" t="s">
         <v>19</v>
       </c>
@@ -39821,7 +39833,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="950" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A950" s="1" t="s">
         <v>19</v>
       </c>
@@ -39859,7 +39871,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="951" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A951" s="1" t="s">
         <v>19</v>
       </c>
@@ -39897,7 +39909,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="952" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A952" s="1" t="s">
         <v>19</v>
       </c>
@@ -39935,7 +39947,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="953" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A953" s="1" t="s">
         <v>19</v>
       </c>
@@ -39973,7 +39985,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="954" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A954" s="1" t="s">
         <v>19</v>
       </c>
@@ -40011,7 +40023,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="955" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A955" s="1" t="s">
         <v>19</v>
       </c>
@@ -40049,7 +40061,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="956" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A956" s="1" t="s">
         <v>19</v>
       </c>
@@ -40087,7 +40099,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="957" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A957" s="1" t="s">
         <v>19</v>
       </c>
@@ -40125,7 +40137,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="958" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A958" s="1" t="s">
         <v>19</v>
       </c>
@@ -40163,7 +40175,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="959" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A959" s="1" t="s">
         <v>19</v>
       </c>
@@ -40201,7 +40213,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="960" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A960" s="1" t="s">
         <v>19</v>
       </c>
@@ -40239,7 +40251,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="961" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A961" s="1" t="s">
         <v>19</v>
       </c>
@@ -40277,7 +40289,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="962" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A962" s="1" t="s">
         <v>19</v>
       </c>
@@ -40315,7 +40327,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="963" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A963" s="1" t="s">
         <v>19</v>
       </c>
@@ -40353,7 +40365,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="964" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A964" s="1" t="s">
         <v>19</v>
       </c>
@@ -40391,7 +40403,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="965" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A965" s="1" t="s">
         <v>19</v>
       </c>
@@ -40429,7 +40441,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="966" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A966" s="1" t="s">
         <v>19</v>
       </c>
@@ -40467,7 +40479,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="967" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F967" s="1" t="s">
         <v>153</v>
       </c>
@@ -40487,7 +40499,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="968" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F968" s="1" t="s">
         <v>111</v>
       </c>
@@ -40510,7 +40522,7 @@
         <v>1027.7</v>
       </c>
     </row>
-    <row r="969" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F969" s="1" t="s">
         <v>153</v>
       </c>
@@ -40530,7 +40542,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="970" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A970" s="1" t="s">
         <v>1276</v>
       </c>
@@ -40568,7 +40580,7 @@
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="971" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F971" s="1" t="s">
         <v>153</v>
       </c>
@@ -40588,7 +40600,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="972" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A972" s="1" t="s">
         <v>1276</v>
       </c>
@@ -40626,7 +40638,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="973" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F973" s="1" t="s">
         <v>153</v>
       </c>
@@ -40646,7 +40658,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="974" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A974" s="1" t="s">
         <v>1276</v>
       </c>
@@ -40684,7 +40696,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="975" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F975" s="1" t="s">
         <v>153</v>
       </c>
@@ -40704,7 +40716,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="976" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A976" s="1" t="s">
         <v>1276</v>
       </c>
@@ -40742,7 +40754,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="977" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F977" s="1" t="s">
         <v>153</v>
       </c>
@@ -40762,7 +40774,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="978" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A978" s="1" t="s">
         <v>1276</v>
       </c>
@@ -40800,7 +40812,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="979" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F979" s="1" t="s">
         <v>153</v>
       </c>
@@ -40820,7 +40832,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="980" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A980" s="1" t="s">
         <v>1276</v>
       </c>
@@ -40858,7 +40870,7 @@
         <v>241.8</v>
       </c>
     </row>
-    <row r="981" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F981" s="1" t="s">
         <v>153</v>
       </c>
@@ -40878,7 +40890,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="982" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A982" s="1" t="s">
         <v>1276</v>
       </c>
@@ -40916,7 +40928,7 @@
         <v>135.30000000000001</v>
       </c>
     </row>
-    <row r="983" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F983" s="1" t="s">
         <v>153</v>
       </c>
@@ -40936,7 +40948,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="984" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A984" s="1" t="s">
         <v>1276</v>
       </c>
@@ -40974,7 +40986,7 @@
         <v>362.1</v>
       </c>
     </row>
-    <row r="985" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F985" s="1" t="s">
         <v>153</v>
       </c>
@@ -40994,7 +41006,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="986" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A986" s="1" t="s">
         <v>1276</v>
       </c>
@@ -41032,7 +41044,7 @@
         <v>54.3</v>
       </c>
     </row>
-    <row r="987" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F987" s="1" t="s">
         <v>153</v>
       </c>
@@ -41052,7 +41064,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="988" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A988" s="1" t="s">
         <v>1276</v>
       </c>
@@ -41090,7 +41102,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="989" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F989" s="1" t="s">
         <v>153</v>
       </c>
@@ -41114,4 +41126,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394D79A8-9E3F-421B-8ED5-700170459604}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>48036</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>